--- a/Connectivity_Application_Data_TEST_ALL_SHEETS36.xlsx
+++ b/Connectivity_Application_Data_TEST_ALL_SHEETS36.xlsx
@@ -65880,7 +65880,11 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
       <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="n"/>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="J4" s="14" t="n"/>
       <c r="K4" s="14" t="n"/>
       <c r="L4" s="14" t="n"/>
@@ -65965,7 +65969,11 @@
       <c r="F5" s="14" t="n"/>
       <c r="G5" s="14" t="n"/>
       <c r="H5" s="14" t="n"/>
-      <c r="I5" s="14" t="n"/>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="J5" s="14" t="n"/>
       <c r="K5" s="14" t="n"/>
       <c r="L5" s="15">
@@ -66049,6 +66057,11 @@
           <t>3x1500MVA ,765/400kV GIS substation at Narela</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66108,6 +66121,11 @@
           <t>Bhadla II - Sikar II 765 kV D/C line (2nd)</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66174,6 +66192,11 @@
           <t>765kV D/C Lakadia PS-Ahmedabad Line</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66240,6 +66263,11 @@
           <t>765kV D/C Ahemdabad- New Navsari (South Gujrat) line</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66306,6 +66334,11 @@
           <t>765/400kV 3x1500MVA Ahmedabad New S/s</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66362,6 +66395,14 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>765/400kV 4x1500MVA KPS2 New SS (GIS)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -66424,6 +66465,14 @@
           <t>7x500 MVA , 400/220 KV Ananthpuram S/s</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66481,6 +66530,11 @@
           <t>Ananthpuram PS-Kurnool-III PS 400 kV (Quad moose) D/c Line</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66542,6 +66596,11 @@
           <t>Ananthpuram PS-Cuddapah-400kV (Quad moose) D/c Line</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66606,6 +66665,11 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>Bhadla-III PS – Sikar-II S/s 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -66677,6 +66741,14 @@
 S/s</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66727,6 +66799,14 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>2x1500MVA, 765/400KV &amp; 2X500MVA, 400/220 kV Ramgarh PS</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -66788,6 +66868,11 @@
           <t>Ramgarh PS- Bhadla-III PS 765kV D/C line</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66855,6 +66940,11 @@
 Ramgarh PS</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -66910,6 +67000,11 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>Beawar-Dausa 765kV D/C line</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -66980,6 +67075,11 @@
           <t>LILO of both circuits of Jaipur (Phagi)-Gwalior 765 kV D/c at Dausa</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67046,6 +67146,11 @@
           <t>LILO of both circuits of Agra – Jaipur (south) 400kV D/c at Dausa</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67106,6 +67211,14 @@
           <t>2x1500MVA, 765/400KV Dausa S/s</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67162,6 +67275,14 @@
         <is>
           <t>Establishment of 765/400 kV 2x1500 MVA, 400/220 kV, 2x500 MVA
 Koppal-II (Phase- A)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -67224,6 +67345,14 @@
 Pooling Station</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67281,6 +67410,11 @@
           <t>Koppal-II PS – Narendra (New) 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67345,6 +67479,11 @@
           <t>Gadag-II PS – Koppal-II PS 400 kV (Quad Moose) D/c line</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67408,6 +67547,11 @@
           <t>Koppal-II PS – Raichur 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67475,6 +67619,14 @@
           <t>Augmentation by 2x1500 MVA, 765/400 kV ICTs at Koppal-II PS</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67532,6 +67684,14 @@
           <t>Augmentation by 2x500 MVA, 400/220 kV ICTs at Koppal-II PS</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67589,6 +67749,11 @@
           <t>Establishment of 765 kV switching station near Vataman</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67641,6 +67806,11 @@
           <t>Halvad – Vataman 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67706,6 +67876,11 @@
 switching station</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67765,6 +67940,11 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>Vataman switching station – Navsari (New)(GIS) 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -67833,6 +68013,14 @@
 Station</t>
         </is>
       </c>
+      <c r="F35" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67890,6 +68078,11 @@
           <t>Bikaner-II PS – Bikaner-III PS 400 kV D/c line (Quad)</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -67952,6 +68145,11 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>Bikaner-III - Neemrana-II 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -68026,6 +68224,11 @@
 Bikaner-III PS</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68090,6 +68293,11 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>Neemrana-II- Bareilly (PG) 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -68161,6 +68369,11 @@
           <t>Bidar PS–Maheshwaram (PG) 765KV D/C line</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68230,6 +68443,14 @@
 MVA, 400/220 kV ICTs</t>
         </is>
       </c>
+      <c r="F41" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68286,6 +68507,11 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>Sikar-II –Narela 765 kV D/C line</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -68354,6 +68580,11 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>Sikar-II –Khetri765 kV D/C line</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -68427,6 +68658,14 @@
 765/400 kV ICT on Bus Section-II (7th &amp; 8th)</t>
         </is>
       </c>
+      <c r="F44" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68478,6 +68717,14 @@
         <is>
           <t>Establishment of 3x1500 MVA, 765/400 kV and 5x500 MVA, 400/220
 kV Mandsaur Pooling Station</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -68540,6 +68787,11 @@
           <t>Mandsaur PS - Indore (PG) 765 kV D/C Line</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68603,6 +68855,11 @@
         <is>
           <t>Establishment of 765 kV Substation at suitable location near
 Rishabdeo (Distt. Udaipur)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -68650,6 +68907,11 @@
           <t>Sirohi PS - Rishabdeo 765 kV D/C line</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68717,6 +68979,11 @@
           <t>Rishabdeo - Mandsaur PS 765 kV D/C line</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68781,6 +69048,11 @@
 Rishabdeo S/S</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68842,6 +69114,14 @@
 location near Sirohi</t>
         </is>
       </c>
+      <c r="F51" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68894,6 +69174,11 @@
           <t>Fatehgarh-IV (Section-2) PS-Sirohi PS 765KV D/C Line</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -68958,6 +69243,11 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>Sirohi PS-Chhitorgarh (PG) 400KV D/C Line (Quad)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -69025,6 +69315,11 @@
           <t>Beawar-Mandsaur PS 765KV D/C line</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69088,6 +69383,11 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>Establishment of 765/400/220/132kV at Kurawar S/s</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -69145,6 +69445,14 @@
           <t>a) 765/400 kV (2x1500 MVA) Kurawar S/s</t>
         </is>
       </c>
+      <c r="F56" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69187,6 +69495,14 @@
           <t>b) 400/220 kV (2x500 MVA) Kurawar S/s</t>
         </is>
       </c>
+      <c r="F57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69229,6 +69545,14 @@
           <t>c) 220/132 kV (3x200 MVA) Kurawar S/s</t>
         </is>
       </c>
+      <c r="F58" t="n">
+        <v>600</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69271,6 +69595,11 @@
           <t>Mandsaur – Kurawar 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69334,6 +69663,11 @@
           <t>Kurawar – Ashta 400 kV D/c line</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69394,6 +69728,11 @@
           <t>Shujalpur – Kurawar 400 kV D/c line</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69454,6 +69793,11 @@
           <t>LILO of one circuit of Indore – Itarsi 400 kV D/c line at Ashta S/s</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69509,6 +69853,11 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>LILO of one circuit of Indore – Bhopal 765 kV S/c line at Kurawar S/s</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -69565,6 +69914,14 @@
 and 6th) (terminated on New 220kV bus section-II)</t>
         </is>
       </c>
+      <c r="F64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69611,6 +69968,14 @@
 (terminated on New 220kV bus section- II)</t>
         </is>
       </c>
+      <c r="F65" t="n">
+        <v>500</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69657,6 +70022,14 @@
 (terminated on New 220kV bus section- III)</t>
         </is>
       </c>
+      <c r="F66" t="n">
+        <v>500</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69703,6 +70076,14 @@
 bus section-III</t>
         </is>
       </c>
+      <c r="F67" t="n">
+        <v>500</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69755,6 +70136,14 @@
           <t>Establishment of 2x1500 MVA, 765/400 kV &amp; 2x500 MVA, 400/220
 kV GIS S/s at a suitable location in South Olpad (between Olpad and
 Ichhapore)</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -69804,6 +70193,11 @@
           <t>Vadodara (GIS) –South Olpad (GIS) 765 kV D/C line</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69865,6 +70259,11 @@
           <t>LILO of Gandhar – Hazira 400 kV D/c line at South Olpad (GIS)</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -69923,6 +70322,11 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>Ahmedabad – South Olpad (GIS) 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -69993,6 +70397,11 @@
           <t>Bhadla-III - Bikaner-III 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70059,6 +70468,14 @@
 kV Barmer-I Pooling Station</t>
         </is>
       </c>
+      <c r="F73" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70102,6 +70519,11 @@
           <t>Fatehgarh-III (Section-2) PS – Barmer-I PS 400 kV D/c line (Quad)</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70160,6 +70582,11 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>Barmer-I PS– Sirohi PS 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -70228,6 +70655,14 @@
 kV Bikaner-IV Pooling Station.</t>
         </is>
       </c>
+      <c r="F76" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70271,6 +70706,11 @@
 PS</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70331,6 +70771,11 @@
           <t>Bikaner-IV PS – Siwani 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70393,6 +70838,11 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>Siwani– Fatehabad (PG) 400 kV D/c line (Quad)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -70459,6 +70909,11 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>Siwani – Patran (Indi Grid) 400 kV D/c line (Quad)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -70529,6 +70984,11 @@
 (2x125 MVAr) at Bikaner-IV PS</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70572,6 +71032,14 @@
 KPS2 and Nagpur terminal station (Bipole-1: 3000 MW)</t>
         </is>
       </c>
+      <c r="F82" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70625,6 +71093,14 @@
 KPS2 and Nagpur terminal station (Bipole-2: 3000 MW)</t>
         </is>
       </c>
+      <c r="F83" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70668,6 +71144,14 @@
 S/s along with associated interconnections with HVDC Switchyard</t>
         </is>
       </c>
+      <c r="F84" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70709,6 +71193,11 @@
         <is>
           <t>±800 kV HVDC Bipole line (Hexa lapwing) between KPS2
 (HVDC) and Nagpur (HVDC)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -70778,6 +71267,11 @@
 lines) at Nagpur</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70837,6 +71331,11 @@
         <is>
           <t>± 300 MVAr STATCOM with 1x125 MVAr MSC, 2x125 MVAr MSR at
 KPS1 400 kV Bus section-1 (GIS)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -70884,6 +71383,11 @@
 KPS1 400 kV Bus section-2 (GIS)</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70929,6 +71433,11 @@
 KPS3 400 kV Bus section-1 (GIS)</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -70982,6 +71491,14 @@
 near Siwani (Distt. Bhiwani)</t>
         </is>
       </c>
+      <c r="F90" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71032,6 +71549,11 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>Bikaner-IV PS – Siwani 765 kV D/C (2nd) line</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -71101,6 +71623,11 @@
           <t>Siwani – Sonipat (PG) 400 kV D/C line (Quad)</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71165,6 +71692,11 @@
           <t>Siwani – Jind (PG) 400 kV D/C line (Quad) (93.69 km).</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71225,6 +71757,11 @@
 (2x125 MVAr) at Siwani S/s.</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71268,6 +71805,14 @@
 III PS</t>
         </is>
       </c>
+      <c r="F95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71325,6 +71870,14 @@
           <t>Augmentation of 1x1500 MVA 765/400 KV (3rd) ICT at Bhadla-III PS</t>
         </is>
       </c>
+      <c r="F96" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71382,6 +71935,14 @@
           <t>Augmentation of 1x1500 MVA 765/400KV (4th) ICT at Bhadla-III PS</t>
         </is>
       </c>
+      <c r="F97" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71438,6 +71999,14 @@
         <is>
           <t>Establishment of 765/400kV, 2x1500 MVA S/s at Ghiror (Distt.
 Mainpuri) (UP)</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -71495,6 +72064,14 @@
 at Barmer-I PS.</t>
         </is>
       </c>
+      <c r="F99" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71538,6 +72115,14 @@
 Barmer-I PS.</t>
         </is>
       </c>
+      <c r="F100" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71578,6 +72163,11 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>Fatehgarh-IV PS (Sec-2) – Barmer-I PS 400kV D/c line.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -71643,6 +72233,11 @@
           <t>Dausa - Ghiror 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71708,6 +72303,11 @@
 S/s</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71772,6 +72372,11 @@
 Ghiror S/s</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71835,6 +72440,11 @@
           <t>400kV Ghiror-Firozabad (UPPTCL) D/c line.</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71894,6 +72504,11 @@
         <is>
           <t>STATCOM (2X±300 MVAr) along with MSC (4X125 MVAr) and MSR
 (2X125 MVAr) at Barmer-I PS</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -71921,6 +72536,11 @@
 (quad) D/c line</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -71984,6 +72604,11 @@
           <t>Gadag-II PS – Koppal-II PS 400 kV (Quad) 2nd D/c line</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72045,6 +72670,14 @@
 Koppal-II PS</t>
         </is>
       </c>
+      <c r="F109" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72093,6 +72726,14 @@
 9th) at Koppal-II PS</t>
         </is>
       </c>
+      <c r="F110" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72141,6 +72782,14 @@
 7th, 8th &amp; 9th) at Gadag-II PS</t>
         </is>
       </c>
+      <c r="F111" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72183,6 +72832,14 @@
           <t>Augmentation by 1x1500 MVA (4th), 765/400kV ICT at Bidar PS</t>
         </is>
       </c>
+      <c r="F112" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72231,6 +72888,14 @@
 Bidar PS</t>
         </is>
       </c>
+      <c r="F113" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72279,6 +72944,14 @@
 Bus section-II</t>
         </is>
       </c>
+      <c r="F114" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72320,6 +72993,14 @@
         <is>
           <t>Augmentation by 1x1500 MVA (9th), 765/400kV ICT at KPS2(GIS) on
 Bus section-I</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -72362,6 +73043,14 @@
 (Raghanesda) PS (GIS) by 2x500 MVA, 400/220 kV ICTs (3rd and 4th)</t>
         </is>
       </c>
+      <c r="F116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72408,6 +73097,14 @@
         <is>
           <t>Establishment of 4x1500 MVA, 765/400 kV and 4x500 MVA, 400/220
 kV Kurnool-IV Pooling Station</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -72455,6 +73152,11 @@
           <t>Kurnool-IV – Bidar 765 kV D/C line</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72515,6 +73217,11 @@
           <t>Kurnool-IV – Kurnool-III PS 765 kV D/C line</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72578,6 +73285,11 @@
           <t>300 MVAr STATCOM at Kurnool-IV PS along with 2x125 MVAr MSR</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72620,6 +73332,14 @@
           <t>Augmentation by 1x1500 MVA, 765/400 kV ICT (3rd) at C’Peta</t>
         </is>
       </c>
+      <c r="F121" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72667,6 +73387,11 @@
           <t>LILO of Vijayawada-Nellore 400 kV D/C line at C’Peta</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72724,6 +73449,14 @@
           <t>Aaugmentation by 4x500 MVA, 400/220 kV ICTs at Sirohi S/s</t>
         </is>
       </c>
+      <c r="F123" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72766,6 +73499,11 @@
           <t>Sirohi – Mandsaur PS 765 kV D/C line</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72827,6 +73565,11 @@
           <t>Mandsaur PS – Khandwa (New) 765 kV D/C line</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72891,6 +73634,14 @@
 Pooling Station near Davanagere / Chitradurga, Karnataka</t>
         </is>
       </c>
+      <c r="F126" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -72932,6 +73683,11 @@
         <is>
           <t>LILO of Narendra New – Madhugiri 765 kV D/C line at Davanagere /
 Chitradurga 765/400 kV PS</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -72993,6 +73749,14 @@
 ICTs</t>
         </is>
       </c>
+      <c r="F128" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73041,6 +73805,11 @@
 (presently charged at 400 kV level) at its rated 765 kV voltage level</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73082,6 +73851,14 @@
         <is>
           <t>Establishment of 4x500 MVA, 400/220 kV Pooling Station near
 Bellary area (Bellary PS), Karnataka</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -73129,6 +73906,11 @@
           <t>Bellary PS – Davanagere / Chitradurga 400 kV D/C line</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73185,6 +73967,14 @@
 Fatehgarh-II PS</t>
         </is>
       </c>
+      <c r="F132" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73228,6 +74018,14 @@
 Fatehgarh-IV PS(Section-II)</t>
         </is>
       </c>
+      <c r="F133" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73271,6 +74069,14 @@
 Barmer-I PS</t>
         </is>
       </c>
+      <c r="F134" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73314,6 +74120,14 @@
 kV ICTs at Kurnool-III PS</t>
         </is>
       </c>
+      <c r="F135" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73361,6 +74175,11 @@
           <t>Kurnool-III PS – Chilakaluripeta 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73421,6 +74240,14 @@
           <t>Augmentation of 1x1500 MVA 765/400 kV ICT (7th) at Kurnool-II PS</t>
         </is>
       </c>
+      <c r="F137" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73467,6 +74294,11 @@
         <is>
           <t>Mahan (existing bus) – Rewa PS (PG) 400 kV D/c (Quad
 ACSR/AAAC/AL59 moose equivalent) line</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -73532,6 +74364,11 @@
 ACSR/AAAC/AL59 moose equivalent) line</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73567,6 +74404,14 @@
 kV ICTs (5th-8th) at Davanagere PS</t>
         </is>
       </c>
+      <c r="F140" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73597,6 +74442,14 @@
 MVA ICTs</t>
         </is>
       </c>
+      <c r="F141" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73628,6 +74481,11 @@
 Projects.</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73664,6 +74522,11 @@
         <is>
           <t>Augmentation of Transformation capacity by 1x1500MVA, 765/400
 kV ICT (4th) (Terminated at 400 kV &amp; 765kV Bus Section-II).</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -73705,6 +74568,11 @@
 II).</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73742,6 +74610,11 @@
           <t>Augmentation of Transformation capacity by 1x500MVA, 400/220kV
 ICT (7th) (Terminated on 400 kV Bus Section-II &amp; 220kV Bus Section-
 III) at Mandsaur PS</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -73774,6 +74647,11 @@
 along with 2x330 MVAr 765 kV Bus reactors</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73808,6 +74686,11 @@
           <t>LILO of 765 kV Fatehpur-Varanasi S/C line at Prayagraj</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73843,6 +74726,11 @@
           <t>LILO of 765 kV Fatehpur-Sasaram S/C line at Prayagraj</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73880,6 +74768,11 @@
 Vindhyachal Pool - Prayagraj D/C line</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73918,6 +74811,11 @@
 line</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73954,6 +74852,11 @@
 SLR at Bidar end on both circuits</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>PGCIL</t>
@@ -73988,6 +74891,11 @@
         <is>
           <t>LILO of one ckt. of Narendra (existing) - Narendra (New) 400kV D/c
 line at Xeldem</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -74056,6 +74964,11 @@
           <t>Xeldem - Mapusa 400kV D/c line</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74109,6 +75022,11 @@
           <t>Xeldem (existing) – Xeldem (new) 220kV D/C line</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74163,6 +75081,11 @@
 line</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74209,6 +75132,11 @@
           <t>2x500MVA, 400/220kV Xeldem</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74257,6 +75185,11 @@
       <c r="E157" t="inlineStr">
         <is>
           <t>Mangalore (Udupi PCL) – Kasargode 400kV D/c line</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -74324,6 +75257,14 @@
           <t>2x500MVA, 400/220 kV Kasargode</t>
         </is>
       </c>
+      <c r="F158" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74373,6 +75314,11 @@
           <t>LILO of one circuit of Kishenpur – Dulhasti 400 kV D/c at Kishtwar</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74429,6 +75375,14 @@
       <c r="E160" t="inlineStr">
         <is>
           <t>7x66.67 MVA, 400/132 kV Kishtwar</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>400</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -74492,6 +75446,11 @@
           <t>Fatehgarh3– Beawar 765kV D/c (2nd)</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74561,6 +75520,11 @@
           <t>Fatehgarh3– Beawar 765kV D/c</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74630,6 +75594,11 @@
           <t>LILO of both circuits of Ajmer – Chittorgarh 765 kV D/c at Beawar</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74698,6 +75667,11 @@
           <t>LILO of of Kota – Merta 400 kV D/c at Beawar</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74766,6 +75740,14 @@
           <t>2X1500MVA , 765/400kV Beawar S/s</t>
         </is>
       </c>
+      <c r="F165" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74824,6 +75806,11 @@
 Fatehgarh-III PS</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74877,6 +75864,14 @@
 unit of 500 MVA) Neemrana-II S/s</t>
         </is>
       </c>
+      <c r="F167" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -74932,6 +75927,11 @@
       <c r="E168" t="inlineStr">
         <is>
           <t>Neemrana-II -Kotputli 400 kV D/c line (Quad)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -75001,6 +76001,11 @@
         <is>
           <t>LILO of both ckts of 400 kV Gurgaon (PG) - Sohna Road (GPTL) D/c
 line (Quad) at Neemrana-II S/s</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -75075,6 +76080,14 @@
 kV Boisar-II (GIS) S/s</t>
         </is>
       </c>
+      <c r="F170" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75132,6 +76145,11 @@
       <c r="E171" t="inlineStr">
         <is>
           <t>South Olpad (GIS) – Boisar-II (GIS) 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -75210,6 +76228,11 @@
           <t>Boisar-II (Sec-II) – Velgaon (MH) 400 kV D/c line</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75280,6 +76303,11 @@
           <t>LILO of Babhaleswar – Padghe (M) 400 kV D/c line at Boisar-II (Sec-I)</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O173" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75350,6 +76378,11 @@
 400 kV level of Navsari (New) (PG) S/s</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75405,6 +76438,11 @@
 Boisar-II.</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75455,6 +76493,11 @@
       <c r="E176" t="inlineStr">
         <is>
           <t>LILO of Navsari (New) – Padghe (PG) 765 kV D/c line at Boisar-II</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -75518,6 +76561,14 @@
 Ananthapuram- II Pooling Station near Kurnool, Andhra Pradesh</t>
         </is>
       </c>
+      <c r="F177" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O177" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75568,6 +76619,11 @@
           <t>Ananthapuram- II - Davangere 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75628,6 +76684,11 @@
           <t>Ananthapuram- II - Cuddapah 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75687,6 +76748,11 @@
 MVAr MSR</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75727,6 +76793,11 @@
 (POWERGRID) 400 kV D/C (Quad) line at Bornagar (ISTS)</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75781,6 +76852,11 @@
 Assam (765 kV and 220 kV levels to be established in future)</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>Sterlite</t>
@@ -75825,6 +76901,11 @@
           <t>NK – Gaya 400kV D/c line</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -75878,6 +76959,11 @@
           <t>NK – Chandwa 400kV D/c line</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -75922,6 +77008,11 @@
 Dhanbad</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -75965,6 +77056,11 @@
           <t>400/220 kV, 2x500 MVA Dhanbad</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -75997,6 +77093,11 @@
       <c r="E187" t="inlineStr">
         <is>
           <t>Narendra New (GIS) – Pune (GIS) 765 D/c Line</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -76063,6 +77164,14 @@
 of 765 kV alongwith 4x1500 MVA transformer</t>
         </is>
       </c>
+      <c r="F188" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76123,6 +77232,11 @@
 MVAr bus reactors</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76180,6 +77294,11 @@
       <c r="E190" t="inlineStr">
         <is>
           <t>KPS2(GIS) - Halvad 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -76252,6 +77371,11 @@
           <t>LILO of Lakadia – Ahmedabad 765 kV D/c line at Halvad</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76313,6 +77437,14 @@
           <t>Augmentation of KPS3 (GIS) by 3x1500 MVA, 765/400 kV ICTs</t>
         </is>
       </c>
+      <c r="F192" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O192" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76368,6 +77500,11 @@
       <c r="E193" t="inlineStr">
         <is>
           <t>765 kV KPS3 (GIS) – Lakadia (AIS) D/C line</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -76440,6 +77577,11 @@
           <t>765 kV KPS1 (GIS)– Bhuj PS D/C line (2nd)</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O194" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76510,6 +77652,11 @@
 KPS3 400 kV.</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O195" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76557,6 +77704,14 @@
         <is>
           <t>Establishment of 4x1500 MVA, 765/400 kV Navinal (Mundra)
 S/s (GIS)</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -76620,6 +77775,11 @@
 (GIS) S/s</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O197" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76689,6 +77849,14 @@
           <t>Establishment of 2x1500 MVA 765/400 kV Jamnagar (GIS) PS</t>
         </is>
       </c>
+      <c r="F198" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O198" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76729,6 +77897,11 @@
       <c r="E199" t="inlineStr">
         <is>
           <t>Halvad – Jamnagar 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -76798,6 +77971,11 @@
 line at Jamnagar</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O200" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76861,6 +78039,11 @@
 moose equivalent) line</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O201" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76924,6 +78107,11 @@
 Jamnagar</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O202" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -76987,6 +78175,11 @@
 Jam Khambhaliya PS</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O203" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77048,6 +78241,11 @@
 Jamnagar 400kV Bus section</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77089,6 +78287,14 @@
         <is>
           <t>Establishment of 2x1500 MVA, 765/400 kV &amp; 3x500 MVA, 400/220
 kV Pune- III (GIS) S/s</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -77138,6 +78344,11 @@
           <t>Boisar-II – Pune-III 765 kV D/c line (228 km)</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O206" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77201,6 +78412,11 @@
 km)</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O207" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77264,6 +78480,11 @@
 km)</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O208" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77324,6 +78545,14 @@
 near Bhadla-III S/s and at Fatehpur(UP) (Bipole-1: 3000 MW)</t>
         </is>
       </c>
+      <c r="F209" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O209" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77368,6 +78597,14 @@
 near Bhadla-III S/s and at Fatehpur(UP) (Bipole-2: 3000 MW)</t>
         </is>
       </c>
+      <c r="F210" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O210" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77411,6 +78648,14 @@
           <t>Establishment of 5x1500 MVA, 765/400 kV ICTs at Fatehpur HVDC</t>
         </is>
       </c>
+      <c r="F211" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O211" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77452,6 +78697,11 @@
         <is>
           <t>±800 kV HVDC line (Hexa lapwing) between Bhadla
 (HVDC) and Fatehpur (HVDC) (with DMR)</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -77510,6 +78760,11 @@
           <t>400 kV 2xD/c Bhadla III-Bhadla (HVDC) line (Quad Moose)</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O213" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77568,6 +78823,11 @@
 Fatehpur</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O214" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77626,6 +78886,14 @@
 Navinal(Mundra) S/s (GIS) by 2x1500 MVA ICTs</t>
         </is>
       </c>
+      <c r="F215" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O215" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77668,6 +78936,11 @@
           <t>Navinal(Mundra) (GIS) – Bhuj 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O216" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77726,6 +78999,11 @@
 MSR at Navinal(Mundra) (GIS) 400 kV Bus section-I</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O217" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77767,6 +79045,11 @@
         <is>
           <t>±300MVAr STATCOM along with 2x125MVAr MSC &amp; 1x125MVAr
 MSR at Navinal(Mundra) (GIS) 400 kV Bus section-II</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -77813,6 +79096,14 @@
 kV bus reactor.</t>
         </is>
       </c>
+      <c r="F219" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O219" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77856,6 +79147,11 @@
 associated bays at South Kalamb S/s.</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O220" t="inlineStr">
         <is>
           <t>Adani</t>
@@ -77913,6 +79209,11 @@
           <t>Koteshwar - Rishikesh 400kV D/C line</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O221" t="inlineStr">
         <is>
           <t>Tata
@@ -77996,6 +79297,11 @@
 Babai.</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O222" t="inlineStr">
         <is>
           <t>Tata
@@ -78048,6 +79354,11 @@
           <t>Babai (RRVPNL) – Bhiwani (PG) 400 kV D/C line</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr">
         <is>
           <t>Tata
@@ -78098,6 +79409,11 @@
       <c r="E224" t="inlineStr">
         <is>
           <t>Bikaner-III - Neemrana-II 765 kV D/C line (2nd)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -78182,6 +79498,14 @@
 Odisha</t>
         </is>
       </c>
+      <c r="F225" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O225" t="inlineStr">
         <is>
           <t>Tata
@@ -78217,6 +79541,11 @@
           <t>Angul - Gopalpur 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O226" t="inlineStr">
         <is>
           <t>Tata
@@ -78276,6 +79605,11 @@
           <t>Gopalpur - Gopalpur (OPTCL) 400 kV D/c (Quad) line</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O227" t="inlineStr">
         <is>
           <t>Tata
@@ -78336,6 +79670,11 @@
 GIS</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O228" t="inlineStr">
         <is>
           <t>Tata
@@ -78377,6 +79716,11 @@
           <t>Extension at 400 kV level at Gopalpur (OPTCL) GIS S/s</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O229" t="inlineStr">
         <is>
           <t>Tata
@@ -78412,6 +79756,14 @@
           <t>Establishment of Paradeep 765/400 kV, 2x1500 MVA GIS substation</t>
         </is>
       </c>
+      <c r="F230" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>Tata
@@ -78455,6 +79807,11 @@
           <t>Angul (POWERGRID) – Paradeep 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O231" t="inlineStr">
         <is>
           <t>Tata
@@ -78520,6 +79877,11 @@
           <t>Paradeep – Paradeep (OPTCL) 400 kV D/c (Quad) line</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O232" t="inlineStr">
         <is>
           <t>Tata
@@ -78590,6 +79952,11 @@
       <c r="E233" t="inlineStr">
         <is>
           <t>Gadag Pooling station – Koppal PS 400 kV D/C line</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -78658,6 +80025,14 @@
       <c r="E234" t="inlineStr">
         <is>
           <t>400/220 kV, 3x500MVA ICT Augmentation at Gadag</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -78710,6 +80085,11 @@
 765 kV S/s</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O235" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -78764,6 +80144,14 @@
         <is>
           <t>2x1500 MVA, 765/400 kV and 2x500 MVA, 400/220 kV S/s at
 Ishanagar (New)</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -78811,6 +80199,11 @@
           <t>Dhule PS – Dhule (BDTCL) 400 kV D/c line</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O237" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -78872,6 +80265,14 @@
           <t>4x500 MVA, 400/220 kV Pooling Station near Dhule (New)</t>
         </is>
       </c>
+      <c r="F238" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O238" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -78918,6 +80319,11 @@
         <is>
           <t>LILO of both circuits of Parli(M) – Karjat(M)/Lonikand-II (M) 400 kV
 D/c line (twin moose) at Kallam PS</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -78976,6 +80382,11 @@
           <t>LILO of 400 kV Kishenpur-Dulhasti line at Kishtwar S/s</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O240" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -79025,6 +80436,11 @@
           <t>400 kV Kishenpur-Samba D/C line .</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O241" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -79081,6 +80497,11 @@
 line (one ckt)</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O242" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -79115,6 +80536,11 @@
           <t>400 kV Samba- Jalandhar D/C line</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -79170,6 +80596,11 @@
 line, thus forming 400 kV Samba – Nakodar direct line</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O244" t="inlineStr">
         <is>
           <t>Indigrid</t>
@@ -79210,6 +80641,11 @@
       <c r="E245" t="inlineStr">
         <is>
           <t>Pachora PS – Ujjain (MPPTCL) 400 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -79287,6 +80723,14 @@
 Pachora PS.</t>
         </is>
       </c>
+      <c r="F246" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O246" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79347,6 +80791,14 @@
 Tumkur, Karnatak</t>
         </is>
       </c>
+      <c r="F247" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O247" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79406,6 +80858,11 @@
 line.</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O248" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79474,6 +80931,14 @@
 Bijapur (Vijayapura), Karnataka</t>
         </is>
       </c>
+      <c r="F249" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O249" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79532,6 +80997,11 @@
           <t>Bijapur PS – Raichur New 400kV (Quad ACSR moose) D/c line</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O250" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79599,6 +81069,14 @@
 and 400/220 kV, 3x500 MVA ICT augmentation at Pachora PS.</t>
         </is>
       </c>
+      <c r="F251" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O251" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79654,6 +81132,11 @@
       <c r="E252" t="inlineStr">
         <is>
           <t>Pachora PS – Rajgarh(PG) 400 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -79715,6 +81198,14 @@
 kV ICTs at Neemuch S/s.</t>
         </is>
       </c>
+      <c r="F253" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O253" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79767,6 +81258,11 @@
           <t>Neemuch PS – Pachora PS 400 kV D/c line.</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O254" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79824,6 +81320,14 @@
           <t>Establishment of 2x500 MVA, 400/220 kV S/s at Handiya.</t>
         </is>
       </c>
+      <c r="F255" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O255" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79881,6 +81385,11 @@
           <t>Pachora PS – Handiya 400 kV D/c line.</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O256" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79938,6 +81447,11 @@
           <t>LILO of Khandwa (PG) – Itarsi (PG) 400 kV D/c line at Handiya S/s.</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O257" t="inlineStr">
         <is>
           <t>GR Infra</t>
@@ -79988,6 +81502,11 @@
       <c r="E258" t="inlineStr">
         <is>
           <t>400 kV D/c Khandukhal (Srinagar) – Rampura (Kashipur) line</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -80065,6 +81584,11 @@
           <t>Fatehgarh 3- Bhadla-3 400kV D/C line (Quad) line</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O259" t="inlineStr">
         <is>
           <t>Apraava
@@ -80139,6 +81663,14 @@
           <t>5x500MVA, 400/220kV pooling station at Fatehgarh-4</t>
         </is>
       </c>
+      <c r="F260" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O260" t="inlineStr">
         <is>
           <t>Apraava
@@ -80195,6 +81727,11 @@
       <c r="E261" t="inlineStr">
         <is>
           <t>Fatehgarh-4 PS- Fatehgarh-3 PS 400kV D/c</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -80263,6 +81800,14 @@
         <is>
           <t>2x1500 MVA, 765/400 kV and 2x500 MVA, 400/220 kV S/s at Karera
 (near Datiya)</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -80305,6 +81850,11 @@
           <t>LILO of Satna-Gwalior 765 kV S/c line at Karera</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O263" t="inlineStr">
         <is>
           <t>Apraava
@@ -80373,6 +81923,14 @@
 MVA, 400/220 kV ICTs at Fatehgarh-IV PS</t>
         </is>
       </c>
+      <c r="F264" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O264" t="inlineStr">
         <is>
           <t>Apraava
@@ -80425,6 +81983,11 @@
         <is>
           <t>Fatehgarh-IV PS (Section-2) - Bhinmal (PG) 400 kV D/C line (Twin
 HTLS)</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -80498,6 +82061,11 @@
 Fatehgarh-IV PS (Section-2)</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O266" t="inlineStr">
         <is>
           <t>Apraava
@@ -80555,6 +82123,14 @@
 alongwith 2x125 MVAR, 420 kV Bus Reactors.</t>
         </is>
       </c>
+      <c r="F267" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O267" t="inlineStr">
         <is>
           <t>Torrent</t>
@@ -80599,6 +82175,11 @@
           <t>Solapur PS – Solapur (PG) 400 kV D/c line</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O268" t="inlineStr">
         <is>
           <t>Torrent</t>
@@ -80656,6 +82237,11 @@
 kV D/c line</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O269" t="inlineStr">
         <is>
           <t>Techno
@@ -80698,6 +82284,11 @@
 D/c line at Gogamukh S/s</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O270" t="inlineStr">
         <is>
           <t>Techno
@@ -80740,6 +82331,14 @@
 MVA, 220/132 kV ICT)</t>
         </is>
       </c>
+      <c r="F271" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O271" t="inlineStr">
         <is>
           <t>Techno
@@ -80778,6 +82377,11 @@
 Bokajan (Assam)</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O272" t="inlineStr">
         <is>
           <t>Techno
@@ -80814,6 +82418,11 @@
 line at Bokajan S/s</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O273" t="inlineStr">
         <is>
           <t>Techno
@@ -80864,6 +82473,14 @@
 Substation</t>
         </is>
       </c>
+      <c r="F274" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O274" t="inlineStr">
         <is>
           <t>DRAIPL</t>
@@ -80931,6 +82548,11 @@
           <t>Merta II- Barmer I PS 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O275" t="inlineStr">
         <is>
           <t>DRAIPL</t>
@@ -81013,6 +82635,11 @@
           <t>Merta II – Beawar 400 kV D/c line (Quad).</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O276" t="inlineStr">
         <is>
           <t>DRAIPL</t>
@@ -81093,6 +82720,11 @@
       <c r="E277" t="inlineStr">
         <is>
           <t>Merta II – Dausa 765 kV D/c line</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -81180,6 +82812,14 @@
 MVAR, 420 kV bus reactor</t>
         </is>
       </c>
+      <c r="F278" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O278" t="inlineStr">
         <is>
           <t>DRAIPL</t>
@@ -81224,6 +82864,11 @@
           <t>Raghanesda (GIS) – Banaskantha (PG) 765 kV D/c line</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O279" t="inlineStr">
         <is>
           <t>DRAIPL</t>
@@ -81272,6 +82917,11 @@
           <t>2 Nos. 765 kV line bays at Banaskantha (PG) S/s</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O280" t="inlineStr">
         <is>
           <t>DRAIPL</t>
@@ -81308,6 +82958,14 @@
         <is>
           <t>Augmentation by 2x500 MVA, 400/220 kV ICTs (3rd &amp; 4th) at
 Lakadia PS</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -81372,6 +83030,14 @@
 Lakadia PS on new 220 kV Bus Section-II</t>
         </is>
       </c>
+      <c r="F282" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O282" t="inlineStr">
         <is>
           <t>Reliance</t>
@@ -81434,6 +83100,14 @@
 new 220 kV Bus Section-II</t>
         </is>
       </c>
+      <c r="F283" t="n">
+        <v>500</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O283" t="inlineStr">
         <is>
           <t>Reliance</t>
@@ -81494,6 +83168,14 @@
 new 220 kV Bus Section-II</t>
         </is>
       </c>
+      <c r="F284" t="n">
+        <v>500</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O284" t="inlineStr">
         <is>
           <t>Reliance</t>
@@ -81552,6 +83234,14 @@
         <is>
           <t>Augmentation of transformation capacity at Lakadia PS by 1x1500
 MVA, 765/400 kV ICT (3rd)</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -81607,6 +83297,11 @@
 2xS/c lines at NLC-Talabira generation switchyard</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O286" t="inlineStr">
         <is>
           <t>HGIEL</t>
@@ -81651,6 +83346,14 @@
 ICT</t>
         </is>
       </c>
+      <c r="F287" t="n">
+        <v>500</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O287" t="inlineStr">
         <is>
           <t>SCL</t>
@@ -81689,6 +83392,14 @@
 and 400/220 kV, 6x500 MVA ICTs</t>
         </is>
       </c>
+      <c r="F288" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O288" t="inlineStr">
         <is>
           <t>SCL</t>
@@ -81727,6 +83438,14 @@
 2x330 MVAr (765 kV) bus reactors</t>
         </is>
       </c>
+      <c r="F289" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O289" t="inlineStr">
         <is>
           <t>SCL</t>
@@ -81765,6 +83484,11 @@
 Ananthapuram-II end on both circuits</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O290" t="inlineStr">
         <is>
           <t>SCL</t>
@@ -81809,6 +83533,11 @@
 CN’Halli</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>TBCB</t>
+        </is>
+      </c>
       <c r="O291" t="inlineStr">
         <is>
           <t>SCL</t>
@@ -81851,6 +83580,11 @@
         <is>
           <t>LILO at CN’Halli of already LILOed section of one circuit of Talaguppa
 - Neelmangala 400 kV line at Hassan</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>TBCB</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
